--- a/registration_forms/039_workforce_housing_manager_contact_form--registration_forms.xlsx
+++ b/registration_forms/039_workforce_housing_manager_contact_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'website'}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Website'}</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'apartments'}</t>
+          <t>apartments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Apartments'}</t>
+          <t>Apartments</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'community_amenities'}</t>
+          <t>community_amenities</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Community Amenities'}</t>
+          <t>Community Amenities</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'housing_options'}</t>
+          <t>housing_options</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Housing Options'}</t>
+          <t>Housing Options</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(tell_us)'}</t>
+          <t>other_(tell_us)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (tell us)'}</t>
+          <t>Other (tell us)</t>
         </is>
       </c>
     </row>
